--- a/public/管理口径原因分析默认模版/上海酒店项目部.xlsx
+++ b/public/管理口径原因分析默认模版/上海酒店项目部.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12255" firstSheet="1" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12255" firstSheet="2" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet sheetId="2" name="目录" state="visible" r:id="rId4"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="98">
   <si>
     <t>工作表目录</t>
   </si>
@@ -68,7 +68,7 @@
     <t>国家管网集团上海区域总部后勤物业服务项目</t>
   </si>
   <si>
-    <t>合计预算执行分析（2026年06月）</t>
+    <t>合计预算执行分析（2026年07月）</t>
   </si>
   <si>
     <t>项目</t>
@@ -245,10 +245,10 @@
     <t>四、净利润</t>
   </si>
   <si>
-    <t>上海酒店租赁项目_合并预算执行分析（2026年06月）</t>
-  </si>
-  <si>
-    <t>租赁户减少，截止至6月空置率29.11%。</t>
+    <t>上海酒店租赁项目_合并预算执行分析（2026年07月）</t>
+  </si>
+  <si>
+    <t>租赁户减少，截止至7月空置率29.11%。</t>
   </si>
   <si>
     <t>租赁收入减少，房产税下降。</t>
@@ -257,19 +257,19 @@
     <t>预算估计不足。</t>
   </si>
   <si>
-    <t>上海酒店租赁项目_222200150213预算执行分析（2026年06月）</t>
-  </si>
-  <si>
-    <t>上海酒店租赁项目_222200150214预算执行分析（2026年06月）</t>
-  </si>
-  <si>
-    <t>上海酒店预算执行分析（2026年06月）</t>
-  </si>
-  <si>
-    <t>餐饮宴会厅收入较同期减少124万元，中餐厅较同期减少73万元</t>
-  </si>
-  <si>
-    <t>受宴会厅装修改造因素影响，宴会收入较预算减少325万元，中餐厅较预算减少95万元</t>
+    <t>上海酒店租赁项目_222200150213预算执行分析（2026年07月）</t>
+  </si>
+  <si>
+    <t>上海酒店租赁项目_222200150214预算执行分析（2026年07月）</t>
+  </si>
+  <si>
+    <t>上海酒店预算执行分析（2026年07月）</t>
+  </si>
+  <si>
+    <t>餐饮宴会厅收入较同期减少155万元，中餐厅较同期减少80万元</t>
+  </si>
+  <si>
+    <t>受宴会厅装修改造因素影响，客房收入减少144万元，宴会收入较预算减少385万元，中餐厅较预算减少113万元，经营性租赁减少60万元。</t>
   </si>
   <si>
     <t>餐饮收入下降同比食材成本下降。</t>
@@ -284,7 +284,7 @@
     <t>与劳务外包合并未超</t>
   </si>
   <si>
-    <t>确认跨期外包费用约50万，财务部组建增加人工约20万元。</t>
+    <t>确认跨期外包费用约50万，财务部组建增加人工约35万元。</t>
   </si>
   <si>
     <t>与用工薪酬合并未超</t>
@@ -308,22 +308,22 @@
     <t>应收账款回收速度加快。</t>
   </si>
   <si>
-    <t>上海酒店能源转售项目预算执行分析（2026年06月）</t>
+    <t>上海酒店能源转售项目预算执行分析（2026年07月）</t>
   </si>
   <si>
     <t>租赁户减少，能源使用下降。</t>
   </si>
   <si>
-    <t>中石化海洋局商城路基地配餐项目预算执行分析（2026年06月）</t>
+    <t>中石化海洋局商城路基地配餐项目预算执行分析（2026年07月）</t>
   </si>
   <si>
     <t>项目已结束</t>
   </si>
   <si>
-    <t>中石化海洋局商城路基地物业服务项目预算执行分析（2026年06月）</t>
-  </si>
-  <si>
-    <t>国家管网集团上海区域总部后勤配餐项目预算执行分析（2026年06月）</t>
+    <t>中石化海洋局商城路基地物业服务项目预算执行分析（2026年07月）</t>
+  </si>
+  <si>
+    <t>国家管网集团上海区域总部后勤配餐项目预算执行分析（2026年07月）</t>
   </si>
   <si>
     <t>国家管网项目4月3日结束，去年同期为整年。</t>
@@ -332,7 +332,7 @@
     <t>国家管网项目4月3日结束，预算为整年。</t>
   </si>
   <si>
-    <t>国家管网集团上海区域总部后勤物业服务项目预算执行分析（2026年06月）</t>
+    <t>国家管网集团上海区域总部后勤物业服务项目预算执行分析（2026年07月）</t>
   </si>
   <si>
     <t>外购燃料为代收代付。</t>
@@ -6457,7 +6457,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" ht="93.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" ht="131.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>28</v>
       </c>
@@ -7416,7 +7416,7 @@
       <c r="M10" s="11"/>
       <c r="N10" s="11"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>36</v>
       </c>
@@ -7425,9 +7425,13 @@
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="12"/>
+      <c r="G11" s="12" t="s">
+        <v>88</v>
+      </c>
       <c r="H11" s="11"/>
-      <c r="I11" s="12"/>
+      <c r="I11" s="12" t="s">
+        <v>88</v>
+      </c>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
       <c r="L11" s="11"/>

--- a/public/管理口径原因分析默认模版/上海酒店项目部.xlsx
+++ b/public/管理口径原因分析默认模版/上海酒店项目部.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12255" firstSheet="2" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet sheetId="2" name="目录" state="visible" r:id="rId4"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="100">
   <si>
     <t>工作表目录</t>
   </si>
@@ -117,9 +117,18 @@
     <t>一、 营业收入</t>
   </si>
   <si>
+    <t>餐饮宴会厅收入较同期减少155万元，中餐厅较同期减少80万元，外接项目结束，租赁户减少，截止至7月空置率29.11%。</t>
+  </si>
+  <si>
+    <t>受宴会厅装修改造因素影响，客房收入减少144万元，宴会收入较预算减少385万元，中餐厅较预算减少113万元，经营性租赁减少60万元。外接项目结束428万元。</t>
+  </si>
+  <si>
     <t xml:space="preserve">     减:（一）经营性采购支出</t>
   </si>
   <si>
+    <t>餐饮收入下降同比食材成本下降。</t>
+  </si>
+  <si>
     <t xml:space="preserve">         其中：1.外购材料</t>
   </si>
   <si>
@@ -147,6 +156,9 @@
     <t xml:space="preserve">                  5.酒店佣金</t>
   </si>
   <si>
+    <t>口径调整在其他固定成本。</t>
+  </si>
+  <si>
     <t xml:space="preserve">        （二）运输费</t>
   </si>
   <si>
@@ -159,12 +171,30 @@
     <t xml:space="preserve">        （五）用工薪酬成本</t>
   </si>
   <si>
+    <t>与劳务外包合并</t>
+  </si>
+  <si>
+    <t>与劳务外包合并未超</t>
+  </si>
+  <si>
     <t xml:space="preserve">        （六）外包劳务支出</t>
   </si>
   <si>
+    <t>确认跨期外包费用约50万，财务部组建增加人工约35万元。</t>
+  </si>
+  <si>
+    <t>与用工薪酬合并未超</t>
+  </si>
+  <si>
     <t xml:space="preserve">        （七）维修费</t>
   </si>
   <si>
+    <t>去年发生较大的零星维护修缮项目，B2楼整体修缮和文化长廊等项目建设费用54万，酒店整体改造项目的前期报告和评估费用（是暂列费）36万。</t>
+  </si>
+  <si>
+    <t>预算中冷水机组的维修，煤气站搬迁、智慧能源管理系统未实施，共计63万元。</t>
+  </si>
+  <si>
     <t xml:space="preserve">        （八）租赁费</t>
   </si>
   <si>
@@ -183,7 +213,13 @@
     <t xml:space="preserve">        （十三）折旧折耗及摊销</t>
   </si>
   <si>
+    <t>员工宿舍租赁口径调整，2025年5月计入此项目。</t>
+  </si>
+  <si>
     <t xml:space="preserve">        （十四）其他固定成本</t>
+  </si>
+  <si>
+    <t>口径调整，实际中含佣金支出。</t>
   </si>
   <si>
     <t xml:space="preserve">        （十五）行政性罚款</t>
@@ -272,37 +308,7 @@
     <t>受宴会厅装修改造因素影响，客房收入减少144万元，宴会收入较预算减少385万元，中餐厅较预算减少113万元，经营性租赁减少60万元。</t>
   </si>
   <si>
-    <t>餐饮收入下降同比食材成本下降。</t>
-  </si>
-  <si>
-    <t>口径调整在其他固定成本。</t>
-  </si>
-  <si>
-    <t>与劳务外包合并</t>
-  </si>
-  <si>
-    <t>与劳务外包合并未超</t>
-  </si>
-  <si>
-    <t>确认跨期外包费用约50万，财务部组建增加人工约35万元。</t>
-  </si>
-  <si>
-    <t>与用工薪酬合并未超</t>
-  </si>
-  <si>
-    <t>去年发生较大的零星维护修缮项目，B2楼整体修缮和文化长廊等项目建设费用54万，酒店整体改造项目的前期报告和评估费用（是暂列费）36万。</t>
-  </si>
-  <si>
-    <t>预算中冷水机组的维修，煤气站搬迁、智慧能源管理系统未实施，共计63万元。</t>
-  </si>
-  <si>
     <t>宴会厅装修改造LED设备使用减少。</t>
-  </si>
-  <si>
-    <t>员工宿舍租赁口径调整，2025年5月计入此项目。</t>
-  </si>
-  <si>
-    <t>口径调整，实际中含佣金支出。</t>
   </si>
   <si>
     <t>应收账款回收速度加快。</t>
@@ -843,7 +849,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -913,7 +919,7 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12"/>
@@ -925,7 +931,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -933,7 +939,7 @@
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="12"/>
@@ -945,7 +951,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -963,7 +969,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -981,7 +987,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -999,7 +1005,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -1017,7 +1023,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -1035,7 +1041,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -1043,7 +1049,7 @@
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H10" s="11"/>
       <c r="I10" s="12"/>
@@ -1055,7 +1061,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -1073,7 +1079,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -1091,7 +1097,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -1109,7 +1115,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -1127,7 +1133,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -1145,7 +1151,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -1163,7 +1169,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -1171,7 +1177,7 @@
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H17" s="11"/>
       <c r="I17" s="12"/>
@@ -1183,7 +1189,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -1191,7 +1197,7 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12"/>
@@ -1203,7 +1209,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -1211,7 +1217,7 @@
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
       <c r="G19" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H19" s="11"/>
       <c r="I19" s="12"/>
@@ -1223,7 +1229,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -1241,7 +1247,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -1249,7 +1255,7 @@
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
       <c r="G21" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H21" s="11"/>
       <c r="I21" s="12"/>
@@ -1261,7 +1267,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -1269,7 +1275,7 @@
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
       <c r="G22" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H22" s="11"/>
       <c r="I22" s="12"/>
@@ -1281,7 +1287,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -1299,7 +1305,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -1317,7 +1323,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -1335,7 +1341,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -1353,7 +1359,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -1371,7 +1377,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -1389,7 +1395,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -1407,7 +1413,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -1425,7 +1431,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -1443,7 +1449,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -1461,7 +1467,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -1479,7 +1485,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -1497,7 +1503,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -1515,7 +1521,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -1533,7 +1539,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -1551,7 +1557,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -1569,7 +1575,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -1587,7 +1593,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -1624,7 +1630,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -1694,11 +1700,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -1708,7 +1714,7 @@
     </row>
     <row r="4" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -1716,11 +1722,11 @@
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
@@ -1730,7 +1736,7 @@
     </row>
     <row r="5" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -1738,11 +1744,11 @@
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
@@ -1752,7 +1758,7 @@
     </row>
     <row r="6" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -1760,11 +1766,11 @@
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
@@ -1774,7 +1780,7 @@
     </row>
     <row r="7" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -1782,11 +1788,11 @@
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H7" s="11"/>
       <c r="I7" s="12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
@@ -1796,7 +1802,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -1814,7 +1820,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -1832,7 +1838,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -1850,7 +1856,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -1868,7 +1874,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -1886,7 +1892,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -1904,7 +1910,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -1922,7 +1928,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -1940,7 +1946,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -1958,7 +1964,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -1976,7 +1982,7 @@
     </row>
     <row r="18" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -1984,11 +1990,11 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -1998,7 +2004,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -2016,7 +2022,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -2034,7 +2040,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -2052,7 +2058,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -2070,7 +2076,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -2088,7 +2094,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -2106,7 +2112,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -2124,7 +2130,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -2142,7 +2148,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -2160,7 +2166,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -2178,7 +2184,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -2196,7 +2202,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -2214,7 +2220,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -2232,7 +2238,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -2250,7 +2256,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -2268,7 +2274,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -2286,7 +2292,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -2304,7 +2310,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -2322,7 +2328,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -2340,7 +2346,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -2358,7 +2364,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -2376,7 +2382,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -2413,7 +2419,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -2483,11 +2489,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -2497,7 +2503,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -2515,7 +2521,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -2533,7 +2539,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -2551,7 +2557,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -2569,7 +2575,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -2587,7 +2593,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -2605,7 +2611,7 @@
     </row>
     <row r="10" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -2615,7 +2621,7 @@
       <c r="G10" s="12"/>
       <c r="H10" s="11"/>
       <c r="I10" s="12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J10" s="11"/>
       <c r="K10" s="11"/>
@@ -2625,7 +2631,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -2643,7 +2649,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -2661,7 +2667,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -2679,7 +2685,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -2697,7 +2703,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -2715,7 +2721,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -2733,7 +2739,7 @@
     </row>
     <row r="17" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -2741,11 +2747,11 @@
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H17" s="11"/>
       <c r="I17" s="12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
@@ -2755,7 +2761,7 @@
     </row>
     <row r="18" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -2763,11 +2769,11 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -2777,7 +2783,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -2795,7 +2801,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -2813,7 +2819,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -2831,7 +2837,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -2849,7 +2855,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -2867,7 +2873,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -2885,7 +2891,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -2903,7 +2909,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -2921,7 +2927,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -2939,7 +2945,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -2957,7 +2963,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -2975,7 +2981,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -2993,7 +2999,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -3011,7 +3017,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -3029,7 +3035,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -3047,7 +3053,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -3065,7 +3071,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -3083,7 +3089,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -3101,7 +3107,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -3119,7 +3125,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -3137,7 +3143,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -3155,7 +3161,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -3389,7 +3395,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" ht="150" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>28</v>
       </c>
@@ -3398,63 +3404,79 @@
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="12"/>
+      <c r="G3" s="12" t="s">
+        <v>29</v>
+      </c>
       <c r="H3" s="11"/>
-      <c r="I3" s="12"/>
+      <c r="I3" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
       <c r="L3" s="11"/>
       <c r="M3" s="11"/>
       <c r="N3" s="11"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="12"/>
+      <c r="G4" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="H4" s="11"/>
-      <c r="I4" s="12"/>
+      <c r="I4" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
       <c r="L4" s="11"/>
       <c r="M4" s="11"/>
       <c r="N4" s="11"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="12"/>
+      <c r="G5" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="H5" s="11"/>
-      <c r="I5" s="12"/>
+      <c r="I5" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
       <c r="L5" s="11"/>
       <c r="M5" s="11"/>
       <c r="N5" s="11"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="12"/>
+      <c r="G6" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="H6" s="11"/>
-      <c r="I6" s="12"/>
+      <c r="I6" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
@@ -3463,7 +3485,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -3481,7 +3503,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -3499,7 +3521,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -3517,7 +3539,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -3535,7 +3557,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -3553,7 +3575,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -3569,18 +3591,22 @@
       <c r="M12" s="11"/>
       <c r="N12" s="11"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="12"/>
+      <c r="G13" s="12" t="s">
+        <v>42</v>
+      </c>
       <c r="H13" s="11"/>
-      <c r="I13" s="12"/>
+      <c r="I13" s="12" t="s">
+        <v>42</v>
+      </c>
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
@@ -3589,7 +3615,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -3607,7 +3633,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -3625,7 +3651,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -3643,52 +3669,64 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="12"/>
+      <c r="G17" s="12" t="s">
+        <v>47</v>
+      </c>
       <c r="H17" s="11"/>
-      <c r="I17" s="12"/>
+      <c r="I17" s="12" t="s">
+        <v>48</v>
+      </c>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="12"/>
+      <c r="G18" s="12" t="s">
+        <v>50</v>
+      </c>
       <c r="H18" s="11"/>
-      <c r="I18" s="12"/>
+      <c r="I18" s="12" t="s">
+        <v>51</v>
+      </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
       <c r="M18" s="11"/>
       <c r="N18" s="11"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" ht="150" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="12"/>
+      <c r="G19" s="12" t="s">
+        <v>53</v>
+      </c>
       <c r="H19" s="11"/>
-      <c r="I19" s="12"/>
+      <c r="I19" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="J19" s="11"/>
       <c r="K19" s="11"/>
       <c r="L19" s="11"/>
@@ -3697,7 +3735,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -3715,7 +3753,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -3733,7 +3771,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -3751,7 +3789,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -3769,7 +3807,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -3785,36 +3823,44 @@
       <c r="M24" s="11"/>
       <c r="N24" s="11"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="12"/>
+      <c r="G25" s="12" t="s">
+        <v>61</v>
+      </c>
       <c r="H25" s="11"/>
-      <c r="I25" s="12"/>
+      <c r="I25" s="12" t="s">
+        <v>61</v>
+      </c>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
       <c r="L25" s="11"/>
       <c r="M25" s="11"/>
       <c r="N25" s="11"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="12"/>
+      <c r="G26" s="12" t="s">
+        <v>63</v>
+      </c>
       <c r="H26" s="11"/>
-      <c r="I26" s="12"/>
+      <c r="I26" s="12" t="s">
+        <v>63</v>
+      </c>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
       <c r="L26" s="11"/>
@@ -3823,7 +3869,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -3841,7 +3887,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -3859,7 +3905,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -3877,7 +3923,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -3895,7 +3941,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -3913,7 +3959,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -3931,7 +3977,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -3949,7 +3995,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -3967,7 +4013,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -3985,7 +4031,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -4003,7 +4049,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -4021,7 +4067,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -4039,7 +4085,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -4057,7 +4103,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -4094,7 +4140,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -4164,11 +4210,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -4178,7 +4224,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -4196,7 +4242,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -4214,7 +4260,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -4232,7 +4278,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -4250,7 +4296,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -4268,7 +4314,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -4286,7 +4332,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -4304,7 +4350,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -4322,7 +4368,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -4340,7 +4386,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -4358,7 +4404,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -4376,7 +4422,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -4394,7 +4440,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -4412,7 +4458,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -4430,7 +4476,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -4448,7 +4494,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -4466,7 +4512,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -4484,7 +4530,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -4502,7 +4548,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -4520,7 +4566,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -4538,7 +4584,7 @@
     </row>
     <row r="24" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -4546,11 +4592,11 @@
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="12" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="H24" s="11"/>
       <c r="I24" s="12" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="J24" s="11"/>
       <c r="K24" s="11"/>
@@ -4560,7 +4606,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -4578,7 +4624,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -4596,7 +4642,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -4614,7 +4660,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -4632,7 +4678,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -4650,7 +4696,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -4668,7 +4714,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -4686,7 +4732,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -4704,7 +4750,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -4722,7 +4768,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -4740,7 +4786,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -4758,7 +4804,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -4776,7 +4822,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -4794,7 +4840,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -4812,7 +4858,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -4830,7 +4876,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -4867,7 +4913,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -4947,7 +4993,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -4965,7 +5011,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -4983,7 +5029,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -5001,7 +5047,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -5019,7 +5065,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -5037,7 +5083,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -5055,7 +5101,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -5073,7 +5119,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -5091,7 +5137,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -5109,7 +5155,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -5127,7 +5173,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -5145,7 +5191,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -5163,7 +5209,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -5181,7 +5227,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -5199,7 +5245,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -5217,7 +5263,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -5235,7 +5281,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -5253,7 +5299,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -5271,7 +5317,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -5289,7 +5335,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -5307,7 +5353,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -5325,7 +5371,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -5343,7 +5389,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -5361,7 +5407,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -5379,7 +5425,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -5397,7 +5443,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -5415,7 +5461,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -5433,7 +5479,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -5451,7 +5497,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -5469,7 +5515,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -5487,7 +5533,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -5505,7 +5551,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -5523,7 +5569,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -5541,7 +5587,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -5559,7 +5605,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -5577,7 +5623,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -5595,7 +5641,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -5632,7 +5678,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -5712,7 +5758,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -5730,7 +5776,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -5748,7 +5794,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -5766,7 +5812,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -5784,7 +5830,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -5802,7 +5848,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -5820,7 +5866,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -5838,7 +5884,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -5856,7 +5902,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -5874,7 +5920,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -5892,7 +5938,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -5910,7 +5956,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -5928,7 +5974,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -5946,7 +5992,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -5964,7 +6010,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -5982,7 +6028,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -6000,7 +6046,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -6018,7 +6064,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -6036,7 +6082,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -6054,7 +6100,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -6072,7 +6118,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -6090,7 +6136,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -6108,7 +6154,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -6126,7 +6172,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -6144,7 +6190,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -6162,7 +6208,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -6180,7 +6226,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -6198,7 +6244,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -6216,7 +6262,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -6234,7 +6280,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -6252,7 +6298,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -6270,7 +6316,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -6288,7 +6334,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -6306,7 +6352,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -6324,7 +6370,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -6342,7 +6388,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -6360,7 +6406,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -6397,7 +6443,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -6467,11 +6513,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -6481,7 +6527,7 @@
     </row>
     <row r="4" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -6489,11 +6535,11 @@
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="12" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="12" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
@@ -6503,7 +6549,7 @@
     </row>
     <row r="5" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -6511,11 +6557,11 @@
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="12" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="12" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
@@ -6525,7 +6571,7 @@
     </row>
     <row r="6" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -6533,11 +6579,11 @@
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="12" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="12" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
@@ -6547,7 +6593,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -6565,7 +6611,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -6583,7 +6629,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -6601,7 +6647,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -6619,7 +6665,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -6637,7 +6683,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -6655,7 +6701,7 @@
     </row>
     <row r="13" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -6663,11 +6709,11 @@
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="12" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="H13" s="11"/>
       <c r="I13" s="12" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
@@ -6677,7 +6723,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -6695,7 +6741,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -6713,7 +6759,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -6731,7 +6777,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -6739,11 +6785,11 @@
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="12" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="H17" s="11"/>
       <c r="I17" s="12" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
@@ -6753,7 +6799,7 @@
     </row>
     <row r="18" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -6761,11 +6807,11 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="12" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -6775,7 +6821,7 @@
     </row>
     <row r="19" ht="150" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -6783,11 +6829,11 @@
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
       <c r="G19" s="12" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="H19" s="11"/>
       <c r="I19" s="12" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="J19" s="11"/>
       <c r="K19" s="11"/>
@@ -6797,7 +6843,7 @@
     </row>
     <row r="20" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -6805,11 +6851,11 @@
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
       <c r="G20" s="12" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H20" s="11"/>
       <c r="I20" s="12" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
@@ -6819,7 +6865,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -6837,7 +6883,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -6855,7 +6901,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -6873,7 +6919,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -6891,7 +6937,7 @@
     </row>
     <row r="25" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -6899,11 +6945,11 @@
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="12" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="H25" s="11"/>
       <c r="I25" s="12" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
@@ -6913,7 +6959,7 @@
     </row>
     <row r="26" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -6921,11 +6967,11 @@
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
       <c r="G26" s="12" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="H26" s="11"/>
       <c r="I26" s="12" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
@@ -6935,7 +6981,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -6953,7 +6999,7 @@
     </row>
     <row r="28" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -6961,7 +7007,7 @@
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H28" s="11"/>
       <c r="I28" s="12"/>
@@ -6973,7 +7019,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -6991,7 +7037,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -7009,7 +7055,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -7027,7 +7073,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -7045,7 +7091,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -7063,7 +7109,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -7081,7 +7127,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -7099,7 +7145,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -7117,7 +7163,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -7135,7 +7181,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -7153,7 +7199,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -7171,7 +7217,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -7208,7 +7254,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -7278,11 +7324,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -7292,7 +7338,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -7310,7 +7356,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -7328,7 +7374,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -7346,7 +7392,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -7364,7 +7410,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -7382,7 +7428,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -7400,7 +7446,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -7418,7 +7464,7 @@
     </row>
     <row r="11" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -7426,11 +7472,11 @@
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H11" s="11"/>
       <c r="I11" s="12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
@@ -7440,7 +7486,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -7458,7 +7504,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -7476,7 +7522,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -7494,7 +7540,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -7512,7 +7558,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -7530,7 +7576,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -7548,7 +7594,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -7566,7 +7612,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -7584,7 +7630,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -7602,7 +7648,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -7620,7 +7666,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -7638,7 +7684,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -7656,7 +7702,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -7674,7 +7720,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -7692,7 +7738,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -7710,7 +7756,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -7728,7 +7774,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -7746,7 +7792,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -7764,7 +7810,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -7782,7 +7828,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -7800,7 +7846,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -7818,7 +7864,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -7836,7 +7882,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -7854,7 +7900,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -7872,7 +7918,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -7890,7 +7936,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -7908,7 +7954,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -7926,7 +7972,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -7944,7 +7990,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -7981,7 +8027,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -8051,7 +8097,7 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12"/>
@@ -8063,7 +8109,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -8071,7 +8117,7 @@
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="12"/>
@@ -8083,7 +8129,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -8091,7 +8137,7 @@
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="12"/>
@@ -8103,7 +8149,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -8111,7 +8157,7 @@
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="12"/>
@@ -8123,7 +8169,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -8141,7 +8187,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -8159,7 +8205,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -8177,7 +8223,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -8195,7 +8241,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -8213,7 +8259,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -8231,7 +8277,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -8249,7 +8295,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -8267,7 +8313,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -8285,7 +8331,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -8303,7 +8349,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -8311,7 +8357,7 @@
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H17" s="11"/>
       <c r="I17" s="12"/>
@@ -8323,7 +8369,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -8331,7 +8377,7 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12"/>
@@ -8343,7 +8389,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -8361,7 +8407,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -8379,7 +8425,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -8397,7 +8443,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -8415,7 +8461,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -8433,7 +8479,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -8451,7 +8497,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -8469,7 +8515,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -8487,7 +8533,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -8505,7 +8551,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -8523,7 +8569,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -8541,7 +8587,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -8559,7 +8605,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -8577,7 +8623,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -8595,7 +8641,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -8613,7 +8659,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -8631,7 +8677,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -8649,7 +8695,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -8667,7 +8713,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -8685,7 +8731,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -8703,7 +8749,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -8721,7 +8767,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
